--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -7242,11 +7242,11 @@
       <c r="E11">
         <v>96</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="6">
         <v>31</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>10</v>
+      <c r="G11" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7265,11 +7265,11 @@
       <c r="E12">
         <v>96</v>
       </c>
-      <c r="F12" s="2">
-        <v>10</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>10</v>
+      <c r="F12" s="6">
+        <v>10</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7403,11 +7403,11 @@
       <c r="E18">
         <v>288</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="6">
         <v>854</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+      <c r="G18" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7518,11 +7518,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="6">
         <v>1775</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -8044,11 +8044,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="6">
         <v>471</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8067,11 +8067,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="6">
         <v>445</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8251,11 +8251,11 @@
       <c r="E23">
         <v>50</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="6">
         <v>14</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="G23" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -8826,11 +8826,11 @@
       <c r="E48">
         <v>100</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="6">
         <v>42</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>10</v>
+      <c r="G48" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -8964,11 +8964,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="2">
+      <c r="F54" s="6">
         <v>751</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="G54" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -9102,11 +9102,11 @@
       <c r="E60">
         <v>100</v>
       </c>
-      <c r="F60" s="2">
+      <c r="F60" s="6">
         <v>645</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>10</v>
+      <c r="G60" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -9194,11 +9194,11 @@
       <c r="E64">
         <v>100</v>
       </c>
-      <c r="F64" s="2">
+      <c r="F64" s="6">
         <v>253</v>
       </c>
-      <c r="G64" s="3" t="s">
-        <v>10</v>
+      <c r="G64" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -9355,11 +9355,11 @@
       <c r="E71">
         <v>100</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="6">
         <v>100</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -9677,11 +9677,11 @@
       <c r="E85">
         <v>100</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="6">
         <v>13</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>10</v>
+      <c r="G85" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -9838,11 +9838,11 @@
       <c r="E92">
         <v>100</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="6">
         <v>940</v>
       </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="G92" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -9976,11 +9976,11 @@
       <c r="E98">
         <v>120</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="6">
         <v>26</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="G98" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -10068,11 +10068,11 @@
       <c r="E102">
         <v>120</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F102" s="6">
         <v>60</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>10</v>
+      <c r="G102" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -10091,11 +10091,11 @@
       <c r="E103">
         <v>120</v>
       </c>
-      <c r="F103" s="2">
+      <c r="F103" s="6">
         <v>335</v>
       </c>
-      <c r="G103" s="3" t="s">
-        <v>10</v>
+      <c r="G103" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -10344,11 +10344,11 @@
       <c r="E114">
         <v>24</v>
       </c>
-      <c r="F114" s="2">
+      <c r="F114" s="6">
         <v>137</v>
       </c>
-      <c r="G114" s="3" t="s">
-        <v>10</v>
+      <c r="G114" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -10643,11 +10643,11 @@
       <c r="E127">
         <v>24</v>
       </c>
-      <c r="F127" s="2">
+      <c r="F127" s="6">
         <v>57</v>
       </c>
-      <c r="G127" s="3" t="s">
-        <v>10</v>
+      <c r="G127" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -10919,11 +10919,11 @@
       <c r="E139">
         <v>30</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="6">
         <v>49</v>
       </c>
-      <c r="G139" s="3" t="s">
-        <v>10</v>
+      <c r="G139" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -10942,11 +10942,11 @@
       <c r="E140">
         <v>30</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="6">
         <v>297</v>
       </c>
-      <c r="G140" s="3" t="s">
-        <v>10</v>
+      <c r="G140" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -10965,11 +10965,11 @@
       <c r="E141">
         <v>30</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="6">
         <v>180</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="G141" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -11356,11 +11356,11 @@
       <c r="E158">
         <v>24</v>
       </c>
-      <c r="F158" s="2">
+      <c r="F158" s="6">
         <v>17</v>
       </c>
-      <c r="G158" s="3" t="s">
-        <v>10</v>
+      <c r="G158" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -11379,11 +11379,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="2">
+      <c r="F159" s="6">
         <v>130</v>
       </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="G159" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -11770,11 +11770,11 @@
       <c r="E176">
         <v>48</v>
       </c>
-      <c r="F176" s="2">
+      <c r="F176" s="6">
         <v>48</v>
       </c>
-      <c r="G176" s="3" t="s">
-        <v>10</v>
+      <c r="G176" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -11793,11 +11793,11 @@
       <c r="E177">
         <v>48</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F177" s="6">
         <v>193</v>
       </c>
-      <c r="G177" s="3" t="s">
-        <v>10</v>
+      <c r="G177" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -11839,11 +11839,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="2">
+      <c r="F179" s="6">
         <v>218</v>
       </c>
-      <c r="G179" s="3" t="s">
-        <v>10</v>
+      <c r="G179" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -11977,11 +11977,11 @@
       <c r="E185">
         <v>240</v>
       </c>
-      <c r="F185" s="2">
+      <c r="F185" s="6">
         <v>1086</v>
       </c>
-      <c r="G185" s="3" t="s">
-        <v>10</v>
+      <c r="G185" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -12299,11 +12299,11 @@
       <c r="E199">
         <v>10</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F199" s="6">
         <v>69</v>
       </c>
-      <c r="G199" s="3" t="s">
-        <v>10</v>
+      <c r="G199" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -12437,11 +12437,11 @@
       <c r="E205">
         <v>280</v>
       </c>
-      <c r="F205" s="2">
+      <c r="F205" s="6">
         <v>745</v>
       </c>
-      <c r="G205" s="3" t="s">
-        <v>10</v>
+      <c r="G205" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -12506,11 +12506,11 @@
       <c r="E208">
         <v>720</v>
       </c>
-      <c r="F208" s="2">
+      <c r="F208" s="6">
         <v>5462</v>
       </c>
-      <c r="G208" s="3" t="s">
-        <v>10</v>
+      <c r="G208" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -12529,11 +12529,11 @@
       <c r="E209">
         <v>720</v>
       </c>
-      <c r="F209" s="2">
+      <c r="F209" s="6">
         <v>6036</v>
       </c>
-      <c r="G209" s="3" t="s">
-        <v>10</v>
+      <c r="G209" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -12575,11 +12575,11 @@
       <c r="E211">
         <v>720</v>
       </c>
-      <c r="F211" s="2">
+      <c r="F211" s="6">
         <v>848</v>
       </c>
-      <c r="G211" s="3" t="s">
-        <v>10</v>
+      <c r="G211" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -12598,11 +12598,11 @@
       <c r="E212">
         <v>720</v>
       </c>
-      <c r="F212" s="2">
+      <c r="F212" s="6">
         <v>4603</v>
       </c>
-      <c r="G212" s="3" t="s">
-        <v>10</v>
+      <c r="G212" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -12621,11 +12621,11 @@
       <c r="E213">
         <v>720</v>
       </c>
-      <c r="F213" s="2">
+      <c r="F213" s="6">
         <v>369</v>
       </c>
-      <c r="G213" s="3" t="s">
-        <v>10</v>
+      <c r="G213" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -12644,11 +12644,11 @@
       <c r="E214">
         <v>720</v>
       </c>
-      <c r="F214" s="2">
+      <c r="F214" s="6">
         <v>3947</v>
       </c>
-      <c r="G214" s="3" t="s">
-        <v>10</v>
+      <c r="G214" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -13817,11 +13817,11 @@
       <c r="E265">
         <v>5</v>
       </c>
-      <c r="F265" s="2">
+      <c r="F265" s="6">
         <v>27</v>
       </c>
-      <c r="G265" s="3" t="s">
-        <v>10</v>
+      <c r="G265" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -13840,11 +13840,11 @@
       <c r="E266">
         <v>5</v>
       </c>
-      <c r="F266" s="2">
+      <c r="F266" s="6">
         <v>26</v>
       </c>
-      <c r="G266" s="3" t="s">
-        <v>10</v>
+      <c r="G266" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -13998,11 +13998,11 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="6">
         <v>115</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -14665,11 +14665,11 @@
       <c r="E35">
         <v>576</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="6">
         <v>2304</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -14711,11 +14711,11 @@
       <c r="E37">
         <v>576</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="6">
         <v>1469</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="G37" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -14734,11 +14734,11 @@
       <c r="E38">
         <v>576</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="6">
         <v>63</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -14803,11 +14803,11 @@
       <c r="E41">
         <v>576</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="6">
         <v>2846</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="G41" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -14826,11 +14826,11 @@
       <c r="E42">
         <v>576</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="6">
         <v>981</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="G42" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -14872,11 +14872,11 @@
       <c r="E44">
         <v>576</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="6">
         <v>125</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>10</v>
+      <c r="G44" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -15766,11 +15766,11 @@
       <c r="E5">
         <v>288</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="6">
         <v>1038</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
+      <c r="G5" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -16157,11 +16157,11 @@
       <c r="E22">
         <v>192</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="6">
         <v>1033</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="G22" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -16295,11 +16295,11 @@
       <c r="E28">
         <v>192</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="6">
         <v>122</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>10</v>
+      <c r="G28" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -16410,11 +16410,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="6">
         <v>1001</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>10</v>
+      <c r="G33" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -16456,11 +16456,11 @@
       <c r="E35">
         <v>144</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="6">
         <v>258</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -16479,11 +16479,11 @@
       <c r="E36">
         <v>72</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="6">
         <v>42</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>10</v>
+      <c r="G36" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -16502,11 +16502,11 @@
       <c r="E37">
         <v>144</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="6">
         <v>344</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>10</v>
+      <c r="G37" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -16525,11 +16525,11 @@
       <c r="E38">
         <v>72</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="6">
         <v>235</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>10</v>
+      <c r="G38" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -16548,11 +16548,11 @@
       <c r="E39">
         <v>144</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="6">
         <v>1014</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>10</v>
+      <c r="G39" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -16571,11 +16571,11 @@
       <c r="E40">
         <v>72</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="6">
         <v>120</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>10</v>
+      <c r="G40" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -16594,11 +16594,11 @@
       <c r="E41">
         <v>144</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="6">
         <v>454</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>10</v>
+      <c r="G41" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -16617,11 +16617,11 @@
       <c r="E42">
         <v>72</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="6">
         <v>60</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>10</v>
+      <c r="G42" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -16640,11 +16640,11 @@
       <c r="E43">
         <v>144</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="6">
         <v>400</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>10</v>
+      <c r="G43" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -16686,11 +16686,11 @@
       <c r="E45">
         <v>144</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="6">
         <v>273</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>10</v>
+      <c r="G45" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -16732,11 +16732,11 @@
       <c r="E47">
         <v>144</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="6">
         <v>1400</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>10</v>
+      <c r="G47" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -17215,11 +17215,11 @@
       <c r="E68">
         <v>200</v>
       </c>
-      <c r="F68" s="2">
+      <c r="F68" s="6">
         <v>44</v>
       </c>
-      <c r="G68" s="3" t="s">
-        <v>10</v>
+      <c r="G68" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -17284,11 +17284,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="2">
+      <c r="F71" s="6">
         <v>1246</v>
       </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="G71" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17353,11 +17353,11 @@
       <c r="E74">
         <v>200</v>
       </c>
-      <c r="F74" s="2">
+      <c r="F74" s="6">
         <v>932</v>
       </c>
-      <c r="G74" s="3" t="s">
-        <v>10</v>
+      <c r="G74" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -17468,11 +17468,11 @@
       <c r="E79">
         <v>200</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="6">
         <v>1865</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="G79" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -17560,11 +17560,11 @@
       <c r="E83">
         <v>1152</v>
       </c>
-      <c r="F83" s="2">
+      <c r="F83" s="6">
         <v>227</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>10</v>
+      <c r="G83" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -17606,11 +17606,11 @@
       <c r="E85">
         <v>1152</v>
       </c>
-      <c r="F85" s="2">
+      <c r="F85" s="6">
         <v>3385</v>
       </c>
-      <c r="G85" s="3" t="s">
-        <v>10</v>
+      <c r="G85" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -17652,11 +17652,11 @@
       <c r="E87">
         <v>576</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="6">
         <v>4143</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="G87" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -17675,11 +17675,11 @@
       <c r="E88">
         <v>576</v>
       </c>
-      <c r="F88" s="2">
+      <c r="F88" s="6">
         <v>5653</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>10</v>
+      <c r="G88" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -17698,11 +17698,11 @@
       <c r="E89">
         <v>576</v>
       </c>
-      <c r="F89" s="2">
+      <c r="F89" s="6">
         <v>207</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>10</v>
+      <c r="G89" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -17721,11 +17721,11 @@
       <c r="E90">
         <v>576</v>
       </c>
-      <c r="F90" s="2">
+      <c r="F90" s="6">
         <v>1132</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>10</v>
+      <c r="G90" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -17767,11 +17767,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="2">
+      <c r="F92" s="6">
         <v>5395</v>
       </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="G92" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -17905,11 +17905,11 @@
       <c r="E98">
         <v>144</v>
       </c>
-      <c r="F98" s="2">
+      <c r="F98" s="6">
         <v>233</v>
       </c>
-      <c r="G98" s="3" t="s">
-        <v>10</v>
+      <c r="G98" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -18181,11 +18181,11 @@
       <c r="E110">
         <v>192</v>
       </c>
-      <c r="F110" s="2">
+      <c r="F110" s="6">
         <v>1359</v>
       </c>
-      <c r="G110" s="3" t="s">
-        <v>10</v>
+      <c r="G110" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -18342,11 +18342,11 @@
       <c r="E117">
         <v>192</v>
       </c>
-      <c r="F117" s="2">
+      <c r="F117" s="6">
         <v>65</v>
       </c>
-      <c r="G117" s="3" t="s">
-        <v>10</v>
+      <c r="G117" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -18411,11 +18411,11 @@
       <c r="E120">
         <v>192</v>
       </c>
-      <c r="F120" s="2">
+      <c r="F120" s="6">
         <v>788</v>
       </c>
-      <c r="G120" s="3" t="s">
-        <v>10</v>
+      <c r="G120" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -18434,11 +18434,11 @@
       <c r="E121">
         <v>192</v>
       </c>
-      <c r="F121" s="2">
+      <c r="F121" s="6">
         <v>137</v>
       </c>
-      <c r="G121" s="3" t="s">
-        <v>10</v>
+      <c r="G121" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -18664,11 +18664,11 @@
       <c r="E131">
         <v>192</v>
       </c>
-      <c r="F131" s="2">
+      <c r="F131" s="6">
         <v>287</v>
       </c>
-      <c r="G131" s="3" t="s">
-        <v>10</v>
+      <c r="G131" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -18710,11 +18710,11 @@
       <c r="E133">
         <v>192</v>
       </c>
-      <c r="F133" s="2">
+      <c r="F133" s="6">
         <v>185</v>
       </c>
-      <c r="G133" s="3" t="s">
-        <v>10</v>
+      <c r="G133" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -18802,11 +18802,11 @@
       <c r="E137">
         <v>192</v>
       </c>
-      <c r="F137" s="2">
+      <c r="F137" s="6">
         <v>108</v>
       </c>
-      <c r="G137" s="3" t="s">
-        <v>10</v>
+      <c r="G137" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -18825,11 +18825,11 @@
       <c r="E138">
         <v>192</v>
       </c>
-      <c r="F138" s="2">
+      <c r="F138" s="6">
         <v>99</v>
       </c>
-      <c r="G138" s="3" t="s">
-        <v>10</v>
+      <c r="G138" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -18848,11 +18848,11 @@
       <c r="E139">
         <v>192</v>
       </c>
-      <c r="F139" s="2">
+      <c r="F139" s="6">
         <v>125</v>
       </c>
-      <c r="G139" s="3" t="s">
-        <v>10</v>
+      <c r="G139" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -18871,11 +18871,11 @@
       <c r="E140">
         <v>192</v>
       </c>
-      <c r="F140" s="2">
+      <c r="F140" s="6">
         <v>17</v>
       </c>
-      <c r="G140" s="3" t="s">
-        <v>10</v>
+      <c r="G140" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -18894,11 +18894,11 @@
       <c r="E141">
         <v>192</v>
       </c>
-      <c r="F141" s="2">
+      <c r="F141" s="6">
         <v>114</v>
       </c>
-      <c r="G141" s="3" t="s">
-        <v>10</v>
+      <c r="G141" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -18917,11 +18917,11 @@
       <c r="E142">
         <v>192</v>
       </c>
-      <c r="F142" s="2">
+      <c r="F142" s="6">
         <v>126</v>
       </c>
-      <c r="G142" s="3" t="s">
-        <v>10</v>
+      <c r="G142" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -18940,11 +18940,11 @@
       <c r="E143">
         <v>192</v>
       </c>
-      <c r="F143" s="2">
+      <c r="F143" s="6">
         <v>42</v>
       </c>
-      <c r="G143" s="3" t="s">
-        <v>10</v>
+      <c r="G143" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -18963,11 +18963,11 @@
       <c r="E144">
         <v>192</v>
       </c>
-      <c r="F144" s="2">
+      <c r="F144" s="6">
         <v>58</v>
       </c>
-      <c r="G144" s="3" t="s">
-        <v>10</v>
+      <c r="G144" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -19788,11 +19788,11 @@
       <c r="E35">
         <v>120</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="6">
         <v>568</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>10</v>
+      <c r="G35" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -20271,11 +20271,11 @@
       <c r="E56">
         <v>144</v>
       </c>
-      <c r="F56" s="2">
+      <c r="F56" s="6">
         <v>19</v>
       </c>
-      <c r="G56" s="3" t="s">
-        <v>10</v>
+      <c r="G56" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -20593,11 +20593,11 @@
       <c r="E70">
         <v>12</v>
       </c>
-      <c r="F70" s="2">
+      <c r="F70" s="6">
         <v>22</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>10</v>
+      <c r="G70" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -20777,11 +20777,11 @@
       <c r="E78">
         <v>144</v>
       </c>
-      <c r="F78" s="2">
+      <c r="F78" s="6">
         <v>936</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>10</v>
+      <c r="G78" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -20800,11 +20800,11 @@
       <c r="E79">
         <v>144</v>
       </c>
-      <c r="F79" s="2">
+      <c r="F79" s="6">
         <v>359</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>10</v>
+      <c r="G79" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -20846,11 +20846,11 @@
       <c r="E81">
         <v>144</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="6">
         <v>319</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>10</v>
+      <c r="G81" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -20984,11 +20984,11 @@
       <c r="E87">
         <v>144</v>
       </c>
-      <c r="F87" s="2">
+      <c r="F87" s="6">
         <v>808</v>
       </c>
-      <c r="G87" s="3" t="s">
-        <v>10</v>
+      <c r="G87" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -21944,11 +21944,11 @@
       <c r="E26">
         <v>24</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="6">
         <v>202</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>10</v>
+      <c r="G26" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -21967,11 +21967,11 @@
       <c r="E27">
         <v>24</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="6">
         <v>198</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>10</v>
+      <c r="G27" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -22674,11 +22674,11 @@
       <c r="E2">
         <v>1000</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="6">
         <v>3238</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -22720,11 +22720,11 @@
       <c r="E4">
         <v>1000</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="6">
         <v>4021</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
+      <c r="G4" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -22766,11 +22766,11 @@
       <c r="E6">
         <v>500</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="6">
         <v>207</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
+      <c r="G6" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -22950,11 +22950,11 @@
       <c r="E14">
         <v>200</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="6">
         <v>1904</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="G14" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -22973,11 +22973,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="6">
         <v>1063</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="G15" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6219,6 +6219,7 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -6786,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>3627</v>
+        <v>3927</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6924,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>25453</v>
+        <v>25578</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14965,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>49096</v>
+        <v>49384</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -19927,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7758</v>
+        <v>7902</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -21393,7 +21394,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1172</v>
+        <v>1184</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21462,7 +21463,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -7198,7 +7198,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>2039</v>
+        <v>2036</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7244,7 +7244,7 @@
         <v>96</v>
       </c>
       <c r="F11" s="6">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>49</v>
@@ -7267,7 +7267,7 @@
         <v>96</v>
       </c>
       <c r="F12" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>49</v>
@@ -7290,7 +7290,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="2">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7405,7 +7405,7 @@
         <v>288</v>
       </c>
       <c r="F18" s="6">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>49</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>46880</v>
+        <v>46870</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>15008</v>
+        <v>14958</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>49742</v>
+        <v>49692</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -9403,7 +9403,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="2">
-        <v>16599</v>
+        <v>16574</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -9426,7 +9426,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="2">
-        <v>47058</v>
+        <v>47033</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -9725,7 +9725,7 @@
         <v>100</v>
       </c>
       <c r="F87" s="2">
-        <v>8930</v>
+        <v>8925</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -9748,7 +9748,7 @@
         <v>100</v>
       </c>
       <c r="F88" s="2">
-        <v>6513</v>
+        <v>6508</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>10</v>
@@ -9771,7 +9771,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="2">
-        <v>12755</v>
+        <v>12750</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -9794,7 +9794,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="2">
-        <v>7711</v>
+        <v>7706</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -9817,7 +9817,7 @@
         <v>100</v>
       </c>
       <c r="F91" s="2">
-        <v>7789</v>
+        <v>7784</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -9840,7 +9840,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="2">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -9863,7 +9863,7 @@
         <v>100</v>
       </c>
       <c r="F93" s="2">
-        <v>11171</v>
+        <v>11166</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -9886,7 +9886,7 @@
         <v>100</v>
       </c>
       <c r="F94" s="2">
-        <v>2807</v>
+        <v>2802</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>10</v>
@@ -9909,7 +9909,7 @@
         <v>100</v>
       </c>
       <c r="F95" s="2">
-        <v>6808</v>
+        <v>6803</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>10</v>
@@ -9932,7 +9932,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="2">
-        <v>15318</v>
+        <v>15313</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="2">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -9978,7 +9978,7 @@
         <v>120</v>
       </c>
       <c r="F98" s="6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G98" s="7" t="s">
         <v>49</v>
@@ -10001,7 +10001,7 @@
         <v>120</v>
       </c>
       <c r="F99" s="2">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="G99" s="3" t="s">
         <v>10</v>
@@ -10024,7 +10024,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="2">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -10047,7 +10047,7 @@
         <v>120</v>
       </c>
       <c r="F101" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>49</v>
@@ -10346,7 +10346,7 @@
         <v>24</v>
       </c>
       <c r="F114" s="2">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G114" s="3" t="s">
         <v>10</v>
@@ -10391,11 +10391,11 @@
       <c r="E116">
         <v>24</v>
       </c>
-      <c r="F116" s="6">
-        <v>3</v>
-      </c>
-      <c r="G116" s="7" t="s">
-        <v>49</v>
+      <c r="F116" s="4">
+        <v>0</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -10438,7 +10438,7 @@
         <v>24</v>
       </c>
       <c r="F118" s="2">
-        <v>2188</v>
+        <v>2182</v>
       </c>
       <c r="G118" s="3" t="s">
         <v>10</v>
@@ -10484,7 +10484,7 @@
         <v>24</v>
       </c>
       <c r="F120" s="2">
-        <v>28796</v>
+        <v>28793</v>
       </c>
       <c r="G120" s="3" t="s">
         <v>10</v>
@@ -10530,7 +10530,7 @@
         <v>24</v>
       </c>
       <c r="F122" s="2">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>10</v>
@@ -10553,7 +10553,7 @@
         <v>24</v>
       </c>
       <c r="F123" s="2">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>10</v>
@@ -10576,7 +10576,7 @@
         <v>24</v>
       </c>
       <c r="F124" s="2">
-        <v>8130</v>
+        <v>8129</v>
       </c>
       <c r="G124" s="3" t="s">
         <v>10</v>
@@ -10645,7 +10645,7 @@
         <v>24</v>
       </c>
       <c r="F127" s="6">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G127" s="7" t="s">
         <v>49</v>
@@ -12600,7 +12600,7 @@
         <v>720</v>
       </c>
       <c r="F212" s="2">
-        <v>4603</v>
+        <v>4601</v>
       </c>
       <c r="G212" s="3" t="s">
         <v>10</v>
@@ -12623,7 +12623,7 @@
         <v>720</v>
       </c>
       <c r="F213" s="6">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G213" s="7" t="s">
         <v>49</v>
@@ -12646,7 +12646,7 @@
         <v>720</v>
       </c>
       <c r="F214" s="2">
-        <v>3947</v>
+        <v>3945</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>10</v>
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>211699</v>
+        <v>211687</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>104351</v>
+        <v>104339</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>15582</v>
+        <v>15579</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14713,7 +14713,7 @@
         <v>576</v>
       </c>
       <c r="F37" s="6">
-        <v>1469</v>
+        <v>1457</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>49</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>9351</v>
+        <v>9345</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>7656</v>
+        <v>7647</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -16159,7 +16159,7 @@
         <v>192</v>
       </c>
       <c r="F22" s="2">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -16181,11 +16181,11 @@
       <c r="E23">
         <v>192</v>
       </c>
-      <c r="F23" s="6">
-        <v>3</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>49</v>
+      <c r="F23" s="4">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -16205,7 +16205,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="2">
-        <v>3521</v>
+        <v>3512</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="2">
-        <v>13784</v>
+        <v>13781</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>11907</v>
+        <v>11901</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>7073</v>
+        <v>7067</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14694</v>
+        <v>14685</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="2">
-        <v>61218</v>
+        <v>61188</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -17470,7 +17470,7 @@
         <v>200</v>
       </c>
       <c r="F79" s="2">
-        <v>1865</v>
+        <v>1855</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>10</v>
@@ -19100,7 +19100,7 @@
         <v>144</v>
       </c>
       <c r="F5" s="2">
-        <v>24538</v>
+        <v>24526</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -19123,7 +19123,7 @@
         <v>144</v>
       </c>
       <c r="F6" s="2">
-        <v>10280</v>
+        <v>10268</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -19169,7 +19169,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>17903</v>
+        <v>17891</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -19261,7 +19261,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="2">
-        <v>3711</v>
+        <v>3709</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -19307,7 +19307,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="2">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -19353,7 +19353,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>49</v>
@@ -19468,7 +19468,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="2">
-        <v>35636</v>
+        <v>35635</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>15899</v>
+        <v>15898</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19514,7 +19514,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -19537,7 +19537,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19560,7 +19560,7 @@
         <v>36</v>
       </c>
       <c r="F25" s="2">
-        <v>13017</v>
+        <v>13016</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -19629,7 +19629,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="2">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -19652,7 +19652,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="2">
-        <v>5347</v>
+        <v>5346</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -19675,7 +19675,7 @@
         <v>48</v>
       </c>
       <c r="F30" s="2">
-        <v>5915</v>
+        <v>5914</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>157701</v>
+        <v>157665</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>40364</v>
+        <v>40352</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>11422</v>
+        <v>11410</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>101264</v>
+        <v>101258</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19882,7 +19882,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="2">
-        <v>16352</v>
+        <v>16346</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7758</v>
+        <v>7743</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>4057</v>
+        <v>4054</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6599</v>
+        <v>6596</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -21394,7 +21394,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21417,7 +21417,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="2">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21440,7 +21440,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -21463,7 +21463,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -21486,7 +21486,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -21923,7 +21923,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -21992,7 +21992,7 @@
         <v>12</v>
       </c>
       <c r="F28" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -22015,7 +22015,7 @@
         <v>12</v>
       </c>
       <c r="F29" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>38568</v>
+        <v>38556</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>92920</v>
+        <v>92896</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>91858</v>
+        <v>91846</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>12961</v>
+        <v>12937</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2">
-        <v>16266</v>
+        <v>16218</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -22906,7 +22906,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="2">
-        <v>15306</v>
+        <v>15281</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>75321</v>
+        <v>74821</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>217243</v>
+        <v>212993</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>3627</v>
+        <v>1627</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>70240</v>
+        <v>69808</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>83953</v>
+        <v>83857</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6879,7 +6879,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>23800</v>
+        <v>22800</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>29904</v>
+        <v>29604</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -7405,7 +7405,7 @@
         <v>288</v>
       </c>
       <c r="F18" s="6">
-        <v>842</v>
+        <v>542</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>49</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>14958</v>
+        <v>11958</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>7989</v>
+        <v>7589</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>14254</v>
+        <v>13954</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8046,7 +8046,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="2">
-        <v>471</v>
+        <v>321</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>5267</v>
+        <v>5117</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>8332</v>
+        <v>8232</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15919</v>
+        <v>15769</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>49692</v>
+        <v>47692</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>8524</v>
+        <v>8424</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>4621</v>
+        <v>4321</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8621,7 +8621,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="2">
-        <v>3223</v>
+        <v>2723</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -8667,7 +8667,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="2">
-        <v>8844</v>
+        <v>8344</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -8736,7 +8736,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="2">
-        <v>3439</v>
+        <v>3139</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="2">
-        <v>3213</v>
+        <v>2713</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="2">
-        <v>1689</v>
+        <v>1189</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -8897,7 +8897,7 @@
         <v>100</v>
       </c>
       <c r="F51" s="2">
-        <v>1492</v>
+        <v>1192</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="2">
-        <v>1217</v>
+        <v>817</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -8965,11 +8965,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="2">
-        <v>751</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>10</v>
+      <c r="F54" s="6">
+        <v>451</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -9012,7 +9012,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="2">
-        <v>6582</v>
+        <v>6082</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>10</v>
@@ -9242,7 +9242,7 @@
         <v>50</v>
       </c>
       <c r="F66" s="2">
-        <v>784</v>
+        <v>584</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -9449,7 +9449,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="2">
-        <v>23876</v>
+        <v>23176</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -9748,7 +9748,7 @@
         <v>100</v>
       </c>
       <c r="F88" s="2">
-        <v>6508</v>
+        <v>6308</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>10</v>
@@ -9771,7 +9771,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="2">
-        <v>12750</v>
+        <v>12650</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -9840,7 +9840,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="2">
-        <v>935</v>
+        <v>835</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -9909,7 +9909,7 @@
         <v>100</v>
       </c>
       <c r="F95" s="2">
-        <v>6803</v>
+        <v>6503</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>10</v>
@@ -9977,11 +9977,11 @@
       <c r="E98">
         <v>120</v>
       </c>
-      <c r="F98" s="6">
-        <v>25</v>
-      </c>
-      <c r="G98" s="7" t="s">
-        <v>49</v>
+      <c r="F98" s="4">
+        <v>0</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -10024,7 +10024,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="2">
-        <v>1440</v>
+        <v>1340</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -10553,7 +10553,7 @@
         <v>24</v>
       </c>
       <c r="F123" s="2">
-        <v>1462</v>
+        <v>1412</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>10</v>
@@ -11128,7 +11128,7 @@
         <v>12</v>
       </c>
       <c r="F148" s="2">
-        <v>172</v>
+        <v>64</v>
       </c>
       <c r="G148" s="3" t="s">
         <v>10</v>
@@ -12209,7 +12209,7 @@
         <v>48</v>
       </c>
       <c r="F195" s="2">
-        <v>2132</v>
+        <v>1432</v>
       </c>
       <c r="G195" s="3" t="s">
         <v>10</v>
@@ -13612,7 +13612,7 @@
         <v>100</v>
       </c>
       <c r="F256" s="2">
-        <v>90955</v>
+        <v>90455</v>
       </c>
       <c r="G256" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>104339</v>
+        <v>104051</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>15578</v>
+        <v>15506</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14092,7 +14092,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="2">
-        <v>2060</v>
+        <v>2024</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -15518,7 +15518,7 @@
         <v>144</v>
       </c>
       <c r="F72" s="2">
-        <v>6387</v>
+        <v>6187</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -15541,7 +15541,7 @@
         <v>144</v>
       </c>
       <c r="F73" s="2">
-        <v>4504</v>
+        <v>4404</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>10</v>
@@ -15564,7 +15564,7 @@
         <v>144</v>
       </c>
       <c r="F74" s="2">
-        <v>10923</v>
+        <v>10823</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>10</v>
@@ -16021,7 +16021,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="2">
-        <v>9675</v>
+        <v>9579</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -16067,7 +16067,7 @@
         <v>192</v>
       </c>
       <c r="F18" s="2">
-        <v>17198</v>
+        <v>17006</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -16895,7 +16895,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="2">
-        <v>7579</v>
+        <v>7483</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>10</v>
@@ -16918,7 +16918,7 @@
         <v>96</v>
       </c>
       <c r="F55" s="2">
-        <v>16418</v>
+        <v>16322</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="2">
-        <v>64226</v>
+        <v>61922</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>20494</v>
+        <v>19918</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="2">
-        <v>5395</v>
+        <v>4243</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -17884,7 +17884,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="2">
-        <v>25960</v>
+        <v>25660</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -18160,7 +18160,7 @@
         <v>192</v>
       </c>
       <c r="F109" s="2">
-        <v>20645</v>
+        <v>20445</v>
       </c>
       <c r="G109" s="3" t="s">
         <v>10</v>
@@ -18206,7 +18206,7 @@
         <v>192</v>
       </c>
       <c r="F111" s="2">
-        <v>25522</v>
+        <v>25422</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>11531</v>
+        <v>11431</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5426</v>
+        <v>5384</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19514,7 +19514,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>708</v>
+        <v>666</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>157665</v>
+        <v>155937</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>11410</v>
+        <v>11290</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7742</v>
+        <v>7442</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6596</v>
+        <v>6496</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20457,7 +20457,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="2">
-        <v>7640</v>
+        <v>7340</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -20710,7 +20710,7 @@
         <v>240</v>
       </c>
       <c r="F75" s="2">
-        <v>9747</v>
+        <v>9447</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>10</v>
@@ -20894,7 +20894,7 @@
         <v>144</v>
       </c>
       <c r="F83" s="2">
-        <v>8199</v>
+        <v>7739</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>10</v>
@@ -20963,7 +20963,7 @@
         <v>144</v>
       </c>
       <c r="F86" s="2">
-        <v>26114</v>
+        <v>25754</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -21009,7 +21009,7 @@
         <v>144</v>
       </c>
       <c r="F88" s="2">
-        <v>8455</v>
+        <v>8155</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>10</v>
@@ -21032,7 +21032,7 @@
         <v>144</v>
       </c>
       <c r="F89" s="2">
-        <v>7086</v>
+        <v>6626</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -21078,7 +21078,7 @@
         <v>144</v>
       </c>
       <c r="F91" s="2">
-        <v>12312</v>
+        <v>11952</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>91846</v>
+        <v>91774</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>12937</v>
+        <v>10937</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2">
-        <v>16216</v>
+        <v>15916</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>20598</v>
+        <v>17523</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22906,7 +22906,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="2">
-        <v>15281</v>
+        <v>15181</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22998,7 +22998,7 @@
         <v>200</v>
       </c>
       <c r="F16" s="2">
-        <v>2947</v>
+        <v>2747</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>74821</v>
+        <v>73971</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>212993</v>
+        <v>210993</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>130113</v>
+        <v>128613</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7037,7 +7037,7 @@
         <v>96</v>
       </c>
       <c r="F2" s="2">
-        <v>10869</v>
+        <v>10845</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7060,7 +7060,7 @@
         <v>96</v>
       </c>
       <c r="F3" s="2">
-        <v>12288</v>
+        <v>12264</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7083,7 +7083,7 @@
         <v>96</v>
       </c>
       <c r="F4" s="2">
-        <v>11433</v>
+        <v>11409</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -7175,7 +7175,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>10076</v>
+        <v>10052</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>11958</v>
+        <v>11708</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>7589</v>
+        <v>7539</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3793</v>
+        <v>3743</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13954</v>
+        <v>13854</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>3159</v>
+        <v>3109</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8046,7 +8046,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="2">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15769</v>
+        <v>15719</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>793</v>
+        <v>743</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>23061</v>
+        <v>23011</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>8424</v>
+        <v>8399</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>18686</v>
+        <v>18661</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8552,7 +8552,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <v>24483</v>
+        <v>24458</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>25356</v>
+        <v>25116</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>38450</v>
+        <v>38414</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -17148,7 +17148,7 @@
         <v>200</v>
       </c>
       <c r="F65" s="2">
-        <v>5330</v>
+        <v>4930</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>7647</v>
+        <v>7447</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17194,7 +17194,7 @@
         <v>200</v>
       </c>
       <c r="F67" s="2">
-        <v>33838</v>
+        <v>33638</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -17240,7 +17240,7 @@
         <v>200</v>
       </c>
       <c r="F69" s="2">
-        <v>25179</v>
+        <v>24979</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="2">
-        <v>11081</v>
+        <v>9581</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -17562,7 +17562,7 @@
         <v>1152</v>
       </c>
       <c r="F83" s="6">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>49</v>
@@ -17608,7 +17608,7 @@
         <v>1152</v>
       </c>
       <c r="F85" s="6">
-        <v>3385</v>
+        <v>3349</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>49</v>
@@ -19514,7 +19514,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>666</v>
+        <v>606</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -19583,7 +19583,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="2">
-        <v>5421</v>
+        <v>5385</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -19652,7 +19652,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="2">
-        <v>5346</v>
+        <v>5310</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>155937</v>
+        <v>153777</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>40352</v>
+        <v>39992</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>11290</v>
+        <v>10930</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>9089</v>
+        <v>9041</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>38556</v>
+        <v>37980</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>73971</v>
+        <v>75638</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>210993</v>
+        <v>235977</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>83362</v>
+        <v>82862</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>69808</v>
+        <v>69708</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>128613</v>
+        <v>128213</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -6971,7 +6971,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="2">
-        <v>114396</v>
+        <v>113896</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7290,7 +7290,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="2">
-        <v>1735</v>
+        <v>1639</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7313,7 +7313,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="2">
-        <v>16202</v>
+        <v>15802</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>40069</v>
+        <v>39569</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7451,7 +7451,7 @@
         <v>72</v>
       </c>
       <c r="F20" s="2">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>11708</v>
+        <v>11704</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -9334,7 +9334,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="2">
-        <v>5567</v>
+        <v>5067</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -9380,7 +9380,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="2">
-        <v>30095</v>
+        <v>30071</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>10</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>43524</v>
+        <v>43324</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -10668,7 +10668,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="2">
-        <v>5434</v>
+        <v>5534</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>10</v>
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -11335,7 +11335,7 @@
         <v>6</v>
       </c>
       <c r="F157" s="2">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>143054</v>
+        <v>141054</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>15506</v>
+        <v>15505</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>16099</v>
+        <v>15523</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>98197</v>
+        <v>98101</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>38414</v>
+        <v>37693</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15745,7 +15745,7 @@
         <v>144</v>
       </c>
       <c r="F4" s="2">
-        <v>27804</v>
+        <v>27803</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -16136,7 +16136,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="2">
-        <v>9267</v>
+        <v>9266</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -16205,7 +16205,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="2">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="2">
-        <v>61188</v>
+        <v>60988</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -17608,7 +17608,7 @@
         <v>1152</v>
       </c>
       <c r="F85" s="6">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>49</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>189585</v>
+        <v>189582</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -18482,7 +18482,7 @@
         <v>192</v>
       </c>
       <c r="F123" s="2">
-        <v>23601</v>
+        <v>23600</v>
       </c>
       <c r="G123" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19537,7 +19537,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>153777</v>
+        <v>153771</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>101258</v>
+        <v>101256</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>5674</v>
+        <v>5656</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6496</v>
+        <v>6526</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20226,11 +20226,11 @@
       <c r="E54">
         <v>144</v>
       </c>
-      <c r="F54" s="4">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>19</v>
+      <c r="F54" s="6">
+        <v>432</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -20342,7 +20342,7 @@
         <v>144</v>
       </c>
       <c r="F59" s="2">
-        <v>4562</v>
+        <v>4550</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>10</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="2">
-        <v>3341</v>
+        <v>3245</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>10</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>120536</v>
+        <v>120176</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>216410</v>
+        <v>215690</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>39219</v>
+        <v>36339</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>37980</v>
+        <v>37974</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>91774</v>
+        <v>91771</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>10937</v>
+        <v>11105</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>17523</v>
+        <v>16723</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>226077</v>
+        <v>225777</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>502</v>
+        <v>377</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>5675</v>
+        <v>5800</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>15778</v>
+        <v>15378</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>38969</v>
+        <v>38769</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -9932,7 +9932,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="2">
-        <v>15313</v>
+        <v>15309</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>14243</v>
+        <v>13881</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94853</v>
+        <v>94832</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>9802</v>
+        <v>9801</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>46934</v>
+        <v>46933</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>37807</v>
+        <v>37374</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>36593</v>
+        <v>36592</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="2">
-        <v>7171</v>
+        <v>5971</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>38191</v>
+        <v>38071</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -20549,7 +20549,7 @@
         <v>12</v>
       </c>
       <c r="F68" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>49</v>
@@ -21147,7 +21147,7 @@
         <v>144</v>
       </c>
       <c r="F94" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>49</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>206682</v>
+        <v>206681</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>36339</v>
+        <v>36051</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>78778</v>
+        <v>78180</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
